--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/47.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/47.xlsx
@@ -426,13 +426,13 @@
         <v>-20.51734439575197</v>
       </c>
       <c r="E2">
-        <v>-27.82197275792263</v>
+        <v>-25.35297174488262</v>
       </c>
       <c r="F2">
-        <v>-3.339545935918256</v>
+        <v>-2.082495088700395</v>
       </c>
       <c r="G2">
-        <v>-18.67327892893119</v>
+        <v>-19.320430992039</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.12401120780948</v>
       </c>
       <c r="E3">
-        <v>-26.51955646247259</v>
+        <v>-26.01119902731953</v>
       </c>
       <c r="F3">
-        <v>-3.128012379204569</v>
+        <v>-1.964914962812228</v>
       </c>
       <c r="G3">
-        <v>-18.87656297777014</v>
+        <v>-18.95476468449881</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.65787762019909</v>
       </c>
       <c r="E4">
-        <v>-27.15426737938767</v>
+        <v>-26.12588716003779</v>
       </c>
       <c r="F4">
-        <v>-3.706414948004907</v>
+        <v>-1.821348951498239</v>
       </c>
       <c r="G4">
-        <v>-19.35339740451906</v>
+        <v>-18.69840265902872</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.15275041531219</v>
       </c>
       <c r="E5">
-        <v>-29.56901727381578</v>
+        <v>-27.28526707548155</v>
       </c>
       <c r="F5">
-        <v>-2.930393738123107</v>
+        <v>-1.647509425081541</v>
       </c>
       <c r="G5">
-        <v>-18.78357968520863</v>
+        <v>-18.06078662234678</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.59426348391237</v>
       </c>
       <c r="E6">
-        <v>-28.07438084216216</v>
+        <v>-27.05608553442736</v>
       </c>
       <c r="F6">
-        <v>-2.839828329975037</v>
+        <v>-1.495002844389138</v>
       </c>
       <c r="G6">
-        <v>-18.72952840818895</v>
+        <v>-18.42246372251216</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.0079776220752</v>
       </c>
       <c r="E7">
-        <v>-29.77869014884493</v>
+        <v>-27.55549470494127</v>
       </c>
       <c r="F7">
-        <v>-2.511451894361674</v>
+        <v>-1.43709913456605</v>
       </c>
       <c r="G7">
-        <v>-18.49101022317554</v>
+        <v>-18.0015129597389</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.41369394536092</v>
       </c>
       <c r="E8">
-        <v>-30.5347800188246</v>
+        <v>-29.09728160796276</v>
       </c>
       <c r="F8">
-        <v>-2.509944265688579</v>
+        <v>-1.555573068881838</v>
       </c>
       <c r="G8">
-        <v>-17.62738324252755</v>
+        <v>-17.18059367182029</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.82318953081535</v>
       </c>
       <c r="E9">
-        <v>-29.81833467454508</v>
+        <v>-28.10824477079152</v>
       </c>
       <c r="F9">
-        <v>-2.352286068118166</v>
+        <v>-1.450610635273112</v>
       </c>
       <c r="G9">
-        <v>-17.85539541127209</v>
+        <v>-17.26908786463054</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.24694512543117</v>
       </c>
       <c r="E10">
-        <v>-29.90853508406686</v>
+        <v>-29.14970775154956</v>
       </c>
       <c r="F10">
-        <v>-2.533427653190542</v>
+        <v>-1.28820340738245</v>
       </c>
       <c r="G10">
-        <v>-17.97881420424889</v>
+        <v>-16.38796961662582</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.72556591383605</v>
       </c>
       <c r="E11">
-        <v>-31.21600515650946</v>
+        <v>-29.76867090010296</v>
       </c>
       <c r="F11">
-        <v>-2.357465021120468</v>
+        <v>-1.156834277707282</v>
       </c>
       <c r="G11">
-        <v>-18.44647676458126</v>
+        <v>-15.81111367749889</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.28173046891645</v>
       </c>
       <c r="E12">
-        <v>-31.80493320120699</v>
+        <v>-30.28299233552412</v>
       </c>
       <c r="F12">
-        <v>-2.160600194375555</v>
+        <v>-1.299408733240119</v>
       </c>
       <c r="G12">
-        <v>-16.15263452114842</v>
+        <v>-15.94491930710516</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.91776985759854</v>
       </c>
       <c r="E13">
-        <v>-32.27758588304658</v>
+        <v>-30.97432729143111</v>
       </c>
       <c r="F13">
-        <v>-1.90950298213676</v>
+        <v>-0.7342119975752104</v>
       </c>
       <c r="G13">
-        <v>-16.8321256483566</v>
+        <v>-15.2445535349991</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.67337169236902</v>
       </c>
       <c r="E14">
-        <v>-33.35790090655342</v>
+        <v>-31.30728107860807</v>
       </c>
       <c r="F14">
-        <v>-1.937173766859875</v>
+        <v>-0.9235800993247886</v>
       </c>
       <c r="G14">
-        <v>-16.17948966656299</v>
+        <v>-15.04000485776415</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.56318360675338</v>
       </c>
       <c r="E15">
-        <v>-33.77527903465538</v>
+        <v>-31.88385997468668</v>
       </c>
       <c r="F15">
-        <v>-2.210692399590243</v>
+        <v>-0.4572382444077648</v>
       </c>
       <c r="G15">
-        <v>-15.17453384157075</v>
+        <v>-14.5673748238501</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.57714436048812</v>
       </c>
       <c r="E16">
-        <v>-32.79593992457156</v>
+        <v>-32.2826758878312</v>
       </c>
       <c r="F16">
-        <v>-1.354137310808276</v>
+        <v>-0.6719552170504107</v>
       </c>
       <c r="G16">
-        <v>-14.84614262152997</v>
+        <v>-14.60422285097496</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.71000629814013</v>
       </c>
       <c r="E17">
-        <v>-33.79599906747747</v>
+        <v>-32.6997891002037</v>
       </c>
       <c r="F17">
-        <v>-2.148264147013065</v>
+        <v>-0.02149545298275212</v>
       </c>
       <c r="G17">
-        <v>-14.9327249742913</v>
+        <v>-14.31080588928382</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.95232278391954</v>
       </c>
       <c r="E18">
-        <v>-36.52094490295701</v>
+        <v>-33.81766781560417</v>
       </c>
       <c r="F18">
-        <v>-1.368980826299041</v>
+        <v>0.05330612349004323</v>
       </c>
       <c r="G18">
-        <v>-14.84135888322573</v>
+        <v>-14.19382941792644</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.26825017623912</v>
       </c>
       <c r="E19">
-        <v>-36.75442170160747</v>
+        <v>-34.30062956852222</v>
       </c>
       <c r="F19">
-        <v>-1.550287256484574</v>
+        <v>0.03883123149352467</v>
       </c>
       <c r="G19">
-        <v>-14.01051623505314</v>
+        <v>-13.96270699164776</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.60570120392771</v>
       </c>
       <c r="E20">
-        <v>-35.17890445993984</v>
+        <v>-34.65578872799579</v>
       </c>
       <c r="F20">
-        <v>-0.8891133884291067</v>
+        <v>0.4354982757936791</v>
       </c>
       <c r="G20">
-        <v>-13.72635224814426</v>
+        <v>-13.43846224223093</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.94017647124975</v>
       </c>
       <c r="E21">
-        <v>-37.23916314481053</v>
+        <v>-35.25416996218433</v>
       </c>
       <c r="F21">
-        <v>-1.093507246498065</v>
+        <v>0.5813630066504357</v>
       </c>
       <c r="G21">
-        <v>-14.54007772060604</v>
+        <v>-13.3400397233484</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.2312928147876</v>
       </c>
       <c r="E22">
-        <v>-38.37781397048418</v>
+        <v>-36.21429249281659</v>
       </c>
       <c r="F22">
-        <v>-1.409560888627383</v>
+        <v>0.3894485035046518</v>
       </c>
       <c r="G22">
-        <v>-13.22068793556659</v>
+        <v>-13.90540475890852</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.43032087701913</v>
       </c>
       <c r="E23">
-        <v>-37.74712886696192</v>
+        <v>-36.77194010330614</v>
       </c>
       <c r="F23">
-        <v>-1.504929170976884</v>
+        <v>0.32950203966626</v>
       </c>
       <c r="G23">
-        <v>-14.27646394513219</v>
+        <v>-13.09003063476818</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.5250553009028</v>
       </c>
       <c r="E24">
-        <v>-38.62744383592</v>
+        <v>-36.30572917574247</v>
       </c>
       <c r="F24">
-        <v>-0.9676393047448887</v>
+        <v>0.6138913378235666</v>
       </c>
       <c r="G24">
-        <v>-14.20427749964838</v>
+        <v>-13.46508564945775</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.50626622278942</v>
       </c>
       <c r="E25">
-        <v>-38.44317570007389</v>
+        <v>-36.43680132742048</v>
       </c>
       <c r="F25">
-        <v>-0.4612409156980921</v>
+        <v>0.6916013122475911</v>
       </c>
       <c r="G25">
-        <v>-14.06941249546955</v>
+        <v>-13.20061278741645</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.36374918258839</v>
       </c>
       <c r="E26">
-        <v>-38.528845371351</v>
+        <v>-36.71824145852318</v>
       </c>
       <c r="F26">
-        <v>-1.000826188003245</v>
+        <v>0.410870084541047</v>
       </c>
       <c r="G26">
-        <v>-13.0134544058993</v>
+        <v>-13.52941120455856</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.10411601556224</v>
       </c>
       <c r="E27">
-        <v>-37.68709035856823</v>
+        <v>-36.85579838498018</v>
       </c>
       <c r="F27">
-        <v>-2.076288960118621</v>
+        <v>0.5450788576730118</v>
       </c>
       <c r="G27">
-        <v>-12.90130636521095</v>
+        <v>-12.78676811064324</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.75418735235102</v>
       </c>
       <c r="E28">
-        <v>-37.85385367813769</v>
+        <v>-36.8518518198825</v>
       </c>
       <c r="F28">
-        <v>-1.719600583412376</v>
+        <v>0.6580938508043511</v>
       </c>
       <c r="G28">
-        <v>-12.61681794483922</v>
+        <v>-12.92155366172913</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.334755837118</v>
       </c>
       <c r="E29">
-        <v>-37.36293313215117</v>
+        <v>-36.66268387516008</v>
       </c>
       <c r="F29">
-        <v>-0.9402302841210586</v>
+        <v>0.3157527975145938</v>
       </c>
       <c r="G29">
-        <v>-13.77822353092633</v>
+        <v>-13.11706454964187</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.85885788645201</v>
       </c>
       <c r="E30">
-        <v>-37.37417959734922</v>
+        <v>-35.95363805740909</v>
       </c>
       <c r="F30">
-        <v>-1.214588881397866</v>
+        <v>0.4419827358227937</v>
       </c>
       <c r="G30">
-        <v>-13.11706786018741</v>
+        <v>-12.70074027425974</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.37068965760148</v>
       </c>
       <c r="E31">
-        <v>-36.54087924553877</v>
+        <v>-36.41412952230107</v>
       </c>
       <c r="F31">
-        <v>-0.9145724321867467</v>
+        <v>0.4940547391301734</v>
       </c>
       <c r="G31">
-        <v>-12.3152769043947</v>
+        <v>-12.7320878299711</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.89772225310539</v>
       </c>
       <c r="E32">
-        <v>-37.99541830409147</v>
+        <v>-35.75023485464357</v>
       </c>
       <c r="F32">
-        <v>-0.6928897180539598</v>
+        <v>0.560674530765518</v>
       </c>
       <c r="G32">
-        <v>-13.62234152839144</v>
+        <v>-13.08172447601015</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.45118365537828</v>
       </c>
       <c r="E33">
-        <v>-39.08195092241085</v>
+        <v>-35.75616262711961</v>
       </c>
       <c r="F33">
-        <v>-1.635225564865427</v>
+        <v>0.6620716710725943</v>
       </c>
       <c r="G33">
-        <v>-13.69558238262951</v>
+        <v>-13.15540397753217</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.0589931480954</v>
       </c>
       <c r="E34">
-        <v>-37.01207828722189</v>
+        <v>-35.33728330988411</v>
       </c>
       <c r="F34">
-        <v>-1.248228053258151</v>
+        <v>0.6763958002018033</v>
       </c>
       <c r="G34">
-        <v>-13.48481319032627</v>
+        <v>-12.92682736077319</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.73820363942003</v>
       </c>
       <c r="E35">
-        <v>-35.51441683493114</v>
+        <v>-35.0442706634548</v>
       </c>
       <c r="F35">
-        <v>-0.5103225126813656</v>
+        <v>0.3296975343733207</v>
       </c>
       <c r="G35">
-        <v>-13.18425869245245</v>
+        <v>-13.13228643803144</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.48577101615738</v>
       </c>
       <c r="E36">
-        <v>-34.97650431416702</v>
+        <v>-34.422708170821</v>
       </c>
       <c r="F36">
-        <v>-1.506945417235298</v>
+        <v>0.1086203568119802</v>
       </c>
       <c r="G36">
-        <v>-13.66736991354384</v>
+        <v>-13.34709780643812</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.29499029467994</v>
       </c>
       <c r="E37">
-        <v>-35.73030277629881</v>
+        <v>-34.16646899757097</v>
       </c>
       <c r="F37">
-        <v>-1.460391997565369</v>
+        <v>0.2329549905025748</v>
       </c>
       <c r="G37">
-        <v>-13.62982501658296</v>
+        <v>-13.18751957980864</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.17072016453347</v>
       </c>
       <c r="E38">
-        <v>-35.81370141786107</v>
+        <v>-33.72128151058791</v>
       </c>
       <c r="F38">
-        <v>-0.9182321593723149</v>
+        <v>0.4418004949941778</v>
       </c>
       <c r="G38">
-        <v>-14.2918579818898</v>
+        <v>-13.34114875610405</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.10043602843758</v>
       </c>
       <c r="E39">
-        <v>-33.6997825802365</v>
+        <v>-33.63110374343617</v>
       </c>
       <c r="F39">
-        <v>-1.311947730616295</v>
+        <v>0.5276798287446109</v>
       </c>
       <c r="G39">
-        <v>-13.20595600791684</v>
+        <v>-13.26452949014316</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.05685699468457</v>
       </c>
       <c r="E40">
-        <v>-35.03707718249362</v>
+        <v>-33.26256973598095</v>
       </c>
       <c r="F40">
-        <v>-1.402103925267382</v>
+        <v>0.7028099515748713</v>
       </c>
       <c r="G40">
-        <v>-14.62028892847704</v>
+        <v>-13.27058116738895</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.04304864924783</v>
       </c>
       <c r="E41">
-        <v>-33.14683552576692</v>
+        <v>-33.06777063382999</v>
       </c>
       <c r="F41">
-        <v>-1.137593788042458</v>
+        <v>0.5547036585261392</v>
       </c>
       <c r="G41">
-        <v>-14.22785851552461</v>
+        <v>-13.18875772384032</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.0490802889619</v>
       </c>
       <c r="E42">
-        <v>-34.72261089045297</v>
+        <v>-32.92455537910042</v>
       </c>
       <c r="F42">
-        <v>-1.444908982439643</v>
+        <v>0.5527122632898092</v>
       </c>
       <c r="G42">
-        <v>-13.6622915366866</v>
+        <v>-13.35271911276381</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.0562317444887</v>
       </c>
       <c r="E43">
-        <v>-33.30612233474972</v>
+        <v>-32.04950249693925</v>
       </c>
       <c r="F43">
-        <v>-1.230898607191586</v>
+        <v>0.7321681206974885</v>
       </c>
       <c r="G43">
-        <v>-13.84387827006116</v>
+        <v>-13.22738516919254</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.06252687590746</v>
       </c>
       <c r="E44">
-        <v>-32.88149864823549</v>
+        <v>-31.79992244471751</v>
       </c>
       <c r="F44">
-        <v>-0.6090365709707742</v>
+        <v>0.4235747553977831</v>
       </c>
       <c r="G44">
-        <v>-14.22713350605151</v>
+        <v>-13.82736692418404</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.07035338649395</v>
       </c>
       <c r="E45">
-        <v>-31.74332104809563</v>
+        <v>-30.84721755450981</v>
       </c>
       <c r="F45">
-        <v>-0.5198255435262815</v>
+        <v>0.6518405052806177</v>
       </c>
       <c r="G45">
-        <v>-13.82071272765011</v>
+        <v>-13.61392281108507</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.07334680405841</v>
       </c>
       <c r="E46">
-        <v>-32.23963500662529</v>
+        <v>-29.96401115489783</v>
       </c>
       <c r="F46">
-        <v>-0.454271032370937</v>
+        <v>0.4361046407325284</v>
       </c>
       <c r="G46">
-        <v>-15.75600799172496</v>
+        <v>-13.7511267156874</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.06318131606916</v>
       </c>
       <c r="E47">
-        <v>-30.76405892206995</v>
+        <v>-29.63259931312048</v>
       </c>
       <c r="F47">
-        <v>-0.6012084990143189</v>
+        <v>0.5563852443538222</v>
       </c>
       <c r="G47">
-        <v>-14.56734833948579</v>
+        <v>-13.36744772986803</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.05351467270334</v>
       </c>
       <c r="E48">
-        <v>-31.72025300150056</v>
+        <v>-30.1196774489115</v>
       </c>
       <c r="F48">
-        <v>-0.4921307361484856</v>
+        <v>0.3985506045266128</v>
       </c>
       <c r="G48">
-        <v>-13.48930229007752</v>
+        <v>-13.86914435361688</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.04631226399977</v>
       </c>
       <c r="E49">
-        <v>-30.43185459734126</v>
+        <v>-29.41544313479366</v>
       </c>
       <c r="F49">
-        <v>-0.322042885699066</v>
+        <v>0.2521076732227022</v>
       </c>
       <c r="G49">
-        <v>-15.28449526693041</v>
+        <v>-13.05966962162752</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.03039571876638</v>
       </c>
       <c r="E50">
-        <v>-29.18950398112896</v>
+        <v>-29.38650165741064</v>
       </c>
       <c r="F50">
-        <v>-0.9111844095092967</v>
+        <v>0.4089043686942038</v>
       </c>
       <c r="G50">
-        <v>-14.64372262507677</v>
+        <v>-13.66777214482686</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.01891369481975</v>
       </c>
       <c r="E51">
-        <v>-30.15373610192318</v>
+        <v>-28.55494250385614</v>
       </c>
       <c r="F51">
-        <v>-0.4866461155745501</v>
+        <v>0.714267929490394</v>
       </c>
       <c r="G51">
-        <v>-15.05829231132309</v>
+        <v>-14.37882270266091</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.01488792151277</v>
       </c>
       <c r="E52">
-        <v>-29.05883486363764</v>
+        <v>-28.24030865827721</v>
       </c>
       <c r="F52">
-        <v>-0.4906065401273346</v>
+        <v>0.5621838161734187</v>
       </c>
       <c r="G52">
-        <v>-15.44684773072181</v>
+        <v>-14.01307032093669</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.00988764825475</v>
       </c>
       <c r="E53">
-        <v>-29.39542727967975</v>
+        <v>-28.34712177469613</v>
       </c>
       <c r="F53">
-        <v>-0.2078333867728897</v>
+        <v>0.4586801375610233</v>
       </c>
       <c r="G53">
-        <v>-15.13246342885769</v>
+        <v>-13.78670845914348</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.00312716563027</v>
       </c>
       <c r="E54">
-        <v>-29.93912945446268</v>
+        <v>-27.74967114191616</v>
       </c>
       <c r="F54">
-        <v>-0.5309306369282116</v>
+        <v>0.5778929756001085</v>
       </c>
       <c r="G54">
-        <v>-15.17161890622342</v>
+        <v>-14.00940554702472</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.00119079050421</v>
       </c>
       <c r="E55">
-        <v>-28.23446692680731</v>
+        <v>-27.98318190412169</v>
       </c>
       <c r="F55">
-        <v>-0.1425994538024286</v>
+        <v>0.4491555691636346</v>
       </c>
       <c r="G55">
-        <v>-15.08808391063099</v>
+        <v>-13.88822633810524</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.00001251569204</v>
       </c>
       <c r="E56">
-        <v>-27.13016684071884</v>
+        <v>-27.09162046996556</v>
       </c>
       <c r="F56">
-        <v>-0.47539605787713</v>
+        <v>0.5970208072981519</v>
       </c>
       <c r="G56">
-        <v>-16.21924931848963</v>
+        <v>-13.79055862360566</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.98646552520637</v>
       </c>
       <c r="E57">
-        <v>-26.64548426767789</v>
+        <v>-26.68665715335563</v>
       </c>
       <c r="F57">
-        <v>-0.4826542130604593</v>
+        <v>0.2693459988749599</v>
       </c>
       <c r="G57">
-        <v>-15.401405527377</v>
+        <v>-14.10341179815786</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.9720462626772</v>
       </c>
       <c r="E58">
-        <v>-26.63109277728151</v>
+        <v>-26.91839728222415</v>
       </c>
       <c r="F58">
-        <v>-0.8731333528617015</v>
+        <v>0.3782945364259565</v>
       </c>
       <c r="G58">
-        <v>-15.39989095279278</v>
+        <v>-14.28609432210593</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.95523529384467</v>
       </c>
       <c r="E59">
-        <v>-25.92558369773051</v>
+        <v>-26.13151605322932</v>
       </c>
       <c r="F59">
-        <v>-0.305859071750572</v>
+        <v>0.3206443070281249</v>
       </c>
       <c r="G59">
-        <v>-15.61065352400495</v>
+        <v>-14.1761312414735</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.92360897157688</v>
       </c>
       <c r="E60">
-        <v>-26.56429778566837</v>
+        <v>-25.84871285145031</v>
       </c>
       <c r="F60">
-        <v>-0.3191336593804341</v>
+        <v>0.4201254335325259</v>
       </c>
       <c r="G60">
-        <v>-15.13366681216121</v>
+        <v>-14.16006847451695</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.88619005469889</v>
       </c>
       <c r="E61">
-        <v>-26.3244969730662</v>
+        <v>-26.30773709076381</v>
       </c>
       <c r="F61">
-        <v>-0.3385464494650405</v>
+        <v>0.5251210018373632</v>
       </c>
       <c r="G61">
-        <v>-16.0629551530351</v>
+        <v>-14.14205910678332</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.84822017219197</v>
       </c>
       <c r="E62">
-        <v>-25.99615543666605</v>
+        <v>-26.08989484862482</v>
       </c>
       <c r="F62">
-        <v>-0.4948163032683616</v>
+        <v>0.3055158331507975</v>
       </c>
       <c r="G62">
-        <v>-14.95575809488078</v>
+        <v>-14.82085336415548</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.80552801797271</v>
       </c>
       <c r="E63">
-        <v>-26.06842988182847</v>
+        <v>-26.19114247048832</v>
       </c>
       <c r="F63">
-        <v>-0.8179599419982404</v>
+        <v>0.2007339836358824</v>
       </c>
       <c r="G63">
-        <v>-15.65527802260155</v>
+        <v>-14.23604218409769</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.75761422083791</v>
       </c>
       <c r="E64">
-        <v>-26.45004438645485</v>
+        <v>-26.43384603492941</v>
       </c>
       <c r="F64">
-        <v>-0.1159500460869658</v>
+        <v>0.2259610845207386</v>
       </c>
       <c r="G64">
-        <v>-15.81071641203418</v>
+        <v>-14.24242160535186</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.71638530233113</v>
       </c>
       <c r="E65">
-        <v>-24.53375721147303</v>
+        <v>-25.44009052784218</v>
       </c>
       <c r="F65">
-        <v>-0.7268461546295172</v>
+        <v>0.2626088867879915</v>
       </c>
       <c r="G65">
-        <v>-15.85661712593618</v>
+        <v>-14.56223023608207</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.68278299270751</v>
       </c>
       <c r="E66">
-        <v>-27.21822301779799</v>
+        <v>-25.84230053225545</v>
       </c>
       <c r="F66">
-        <v>-0.7069297171640087</v>
+        <v>0.2466131122399331</v>
       </c>
       <c r="G66">
-        <v>-16.1866354791095</v>
+        <v>-14.81077771880671</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.64588540699224</v>
       </c>
       <c r="E67">
-        <v>-26.51776771523956</v>
+        <v>-26.4378537344262</v>
       </c>
       <c r="F67">
-        <v>-0.7274226983418656</v>
+        <v>0.4298869150071153</v>
       </c>
       <c r="G67">
-        <v>-16.39437883278985</v>
+        <v>-14.75002093179723</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.61959340226809</v>
       </c>
       <c r="E68">
-        <v>-25.30941235340284</v>
+        <v>-25.23137316082866</v>
       </c>
       <c r="F68">
-        <v>-0.6365350552741067</v>
+        <v>0.08815554012581843</v>
       </c>
       <c r="G68">
-        <v>-15.38846129431845</v>
+        <v>-15.15283487083359</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.60387583851409</v>
       </c>
       <c r="E69">
-        <v>-26.32059795694559</v>
+        <v>-26.10491579690827</v>
       </c>
       <c r="F69">
-        <v>-1.104142655582608</v>
+        <v>0.03714301872661928</v>
       </c>
       <c r="G69">
-        <v>-15.1127888567178</v>
+        <v>-14.46997857408474</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.58665047665876</v>
       </c>
       <c r="E70">
-        <v>-25.91669430325346</v>
+        <v>-25.12139916955238</v>
       </c>
       <c r="F70">
-        <v>-0.8995591013784084</v>
+        <v>0.3197670659485602</v>
       </c>
       <c r="G70">
-        <v>-15.34060901382106</v>
+        <v>-14.2185095349217</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.57030067463241</v>
       </c>
       <c r="E71">
-        <v>-26.10912274926139</v>
+        <v>-25.51322085459205</v>
       </c>
       <c r="F71">
-        <v>-1.354697287172569</v>
+        <v>0.1235566494518581</v>
       </c>
       <c r="G71">
-        <v>-14.46303636008889</v>
+        <v>-14.09797919292792</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.55633662986541</v>
       </c>
       <c r="E72">
-        <v>-26.50690390609516</v>
+        <v>-25.34552693361401</v>
       </c>
       <c r="F72">
-        <v>-1.268388030740083</v>
+        <v>0.02461396175927676</v>
       </c>
       <c r="G72">
-        <v>-15.42568837890756</v>
+        <v>-14.46545967942364</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.53618053441332</v>
       </c>
       <c r="E73">
-        <v>-26.22563585700474</v>
+        <v>-25.55104266950411</v>
       </c>
       <c r="F73">
-        <v>-0.9620469964085892</v>
+        <v>-0.1174411074120049</v>
       </c>
       <c r="G73">
-        <v>-14.60180946327683</v>
+        <v>-14.66218057173098</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.5008243368895</v>
       </c>
       <c r="E74">
-        <v>-25.46450805969154</v>
+        <v>-25.18104822918141</v>
       </c>
       <c r="F74">
-        <v>-0.5302729132103888</v>
+        <v>-0.1407356271461297</v>
       </c>
       <c r="G74">
-        <v>-14.34601354109397</v>
+        <v>-14.46236100879888</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.45729761220136</v>
       </c>
       <c r="E75">
-        <v>-25.26511934913382</v>
+        <v>-25.66253822804697</v>
       </c>
       <c r="F75">
-        <v>-1.233090467339393</v>
+        <v>-0.1271835364363298</v>
       </c>
       <c r="G75">
-        <v>-15.45518533966246</v>
+        <v>-13.9230350691779</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.40215111118257</v>
       </c>
       <c r="E76">
-        <v>-26.60365022479503</v>
+        <v>-26.06196774941952</v>
       </c>
       <c r="F76">
-        <v>-1.357330667146069</v>
+        <v>-0.3571424692904866</v>
       </c>
       <c r="G76">
-        <v>-13.99389895171877</v>
+        <v>-14.01803282870006</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.32137405065162</v>
       </c>
       <c r="E77">
-        <v>-26.41996173362189</v>
+        <v>-26.3943984978486</v>
       </c>
       <c r="F77">
-        <v>-1.208126787288627</v>
+        <v>-0.1174692719037</v>
       </c>
       <c r="G77">
-        <v>-13.49276677598437</v>
+        <v>-13.89261943203585</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.22598816796009</v>
       </c>
       <c r="E78">
-        <v>-27.14412812608449</v>
+        <v>-26.40221464398583</v>
       </c>
       <c r="F78">
-        <v>-1.235695682821198</v>
+        <v>-0.3175647315195319</v>
       </c>
       <c r="G78">
-        <v>-14.82612209738123</v>
+        <v>-13.6648423120246</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.1170830427459</v>
       </c>
       <c r="E79">
-        <v>-26.54071349303642</v>
+        <v>-26.58730243362734</v>
       </c>
       <c r="F79">
-        <v>-1.770853331358387</v>
+        <v>-0.2983126447110685</v>
       </c>
       <c r="G79">
-        <v>-14.63370822482048</v>
+        <v>-13.74385179186485</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.98728295898304</v>
       </c>
       <c r="E80">
-        <v>-27.46600300160168</v>
+        <v>-27.49947748146639</v>
       </c>
       <c r="F80">
-        <v>-1.53096972865129</v>
+        <v>-0.447908342350034</v>
       </c>
       <c r="G80">
-        <v>-13.15323888074948</v>
+        <v>-13.41486136308147</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.84108219962494</v>
       </c>
       <c r="E81">
-        <v>-29.02656042938497</v>
+        <v>-26.9292927906866</v>
       </c>
       <c r="F81">
-        <v>-0.9281709114711034</v>
+        <v>-0.2885983801784387</v>
       </c>
       <c r="G81">
-        <v>-13.16994058299511</v>
+        <v>-13.74307546893589</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.68687630063891</v>
       </c>
       <c r="E82">
-        <v>-29.17634876413668</v>
+        <v>-27.80533967289245</v>
       </c>
       <c r="F82">
-        <v>-1.722851097100962</v>
+        <v>-0.6103271673843359</v>
       </c>
       <c r="G82">
-        <v>-13.76784331538795</v>
+        <v>-13.5597457333349</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.5247526200194</v>
       </c>
       <c r="E83">
-        <v>-30.32951108476791</v>
+        <v>-28.3563145769317</v>
       </c>
       <c r="F83">
-        <v>-1.341891555492691</v>
+        <v>-0.6647103157455262</v>
       </c>
       <c r="G83">
-        <v>-15.02710862761592</v>
+        <v>-13.66044259700291</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.35188410647145</v>
       </c>
       <c r="E84">
-        <v>-29.04829257614778</v>
+        <v>-29.1922980495917</v>
       </c>
       <c r="F84">
-        <v>-1.509231711267025</v>
+        <v>-0.7256789849589727</v>
       </c>
       <c r="G84">
-        <v>-13.32156356869373</v>
+        <v>-12.98887029472467</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.18525274579707</v>
       </c>
       <c r="E85">
-        <v>-29.52596733566186</v>
+        <v>-30.21234134829345</v>
       </c>
       <c r="F85">
-        <v>-2.020861240462501</v>
+        <v>-0.7839132133757779</v>
       </c>
       <c r="G85">
-        <v>-13.04074654332505</v>
+        <v>-13.24647377477198</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.03152834821973</v>
       </c>
       <c r="E86">
-        <v>-31.84960659729266</v>
+        <v>-30.75978404260671</v>
       </c>
       <c r="F86">
-        <v>-1.775842588225449</v>
+        <v>-0.6356934339928624</v>
       </c>
       <c r="G86">
-        <v>-13.85046625568431</v>
+        <v>-13.13506398573888</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.886460195547681</v>
       </c>
       <c r="E87">
-        <v>-32.87628637465266</v>
+        <v>-31.26993928194081</v>
       </c>
       <c r="F87">
-        <v>-1.836764040496936</v>
+        <v>-0.7714736200879377</v>
       </c>
       <c r="G87">
-        <v>-12.0455435854915</v>
+        <v>-13.13170047147099</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.767637764363352</v>
       </c>
       <c r="E88">
-        <v>-33.14225497430816</v>
+        <v>-32.68572139569888</v>
       </c>
       <c r="F88">
-        <v>-2.655030331186704</v>
+        <v>-0.9736830733157138</v>
       </c>
       <c r="G88">
-        <v>-12.72195425007539</v>
+        <v>-12.81514610700587</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.685265169910675</v>
       </c>
       <c r="E89">
-        <v>-34.12627652651589</v>
+        <v>-33.90901166481289</v>
       </c>
       <c r="F89">
-        <v>-3.234173460445145</v>
+        <v>-1.119237166396421</v>
       </c>
       <c r="G89">
-        <v>-13.70793237276376</v>
+        <v>-12.79653753052963</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.639355170017405</v>
       </c>
       <c r="E90">
-        <v>-34.48899597334528</v>
+        <v>-34.08281676146429</v>
       </c>
       <c r="F90">
-        <v>-2.365800053927437</v>
+        <v>-1.023497775450465</v>
       </c>
       <c r="G90">
-        <v>-13.0470564431229</v>
+        <v>-12.99407116176686</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.63415474908534</v>
       </c>
       <c r="E91">
-        <v>-35.13958824860525</v>
+        <v>-36.22053046576216</v>
       </c>
       <c r="F91">
-        <v>-2.458178758320235</v>
+        <v>-1.182939448039105</v>
       </c>
       <c r="G91">
-        <v>-13.14614107111329</v>
+        <v>-12.1680139071713</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.681705133502073</v>
       </c>
       <c r="E92">
-        <v>-37.62374379991193</v>
+        <v>-36.42119620599005</v>
       </c>
       <c r="F92">
-        <v>-2.660435428489971</v>
+        <v>-1.38760749571839</v>
       </c>
       <c r="G92">
-        <v>-12.49763168433437</v>
+        <v>-12.67309390846129</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.783064491166162</v>
       </c>
       <c r="E93">
-        <v>-37.6318746749927</v>
+        <v>-38.5490989713503</v>
       </c>
       <c r="F93">
-        <v>-2.965001271477265</v>
+        <v>-1.422627556039142</v>
       </c>
       <c r="G93">
-        <v>-12.98772815651362</v>
+        <v>-12.36264750051613</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.926915016851106</v>
       </c>
       <c r="E94">
-        <v>-39.82664941602422</v>
+        <v>-39.54604931684995</v>
       </c>
       <c r="F94">
-        <v>-3.36238154011123</v>
+        <v>-1.852679463406922</v>
       </c>
       <c r="G94">
-        <v>-12.50118058915247</v>
+        <v>-12.8029335045115</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.12446751267837</v>
       </c>
       <c r="E95">
-        <v>-41.03845321081779</v>
+        <v>-41.72119085882121</v>
       </c>
       <c r="F95">
-        <v>-3.000102511803491</v>
+        <v>-1.779987738709057</v>
       </c>
       <c r="G95">
-        <v>-13.17349941944982</v>
+        <v>-12.71069839524187</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.37722605534367</v>
       </c>
       <c r="E96">
-        <v>-41.34650491942656</v>
+        <v>-42.99450265182396</v>
       </c>
       <c r="F96">
-        <v>-4.235370609797337</v>
+        <v>-2.188998285678327</v>
       </c>
       <c r="G96">
-        <v>-11.60584685860212</v>
+        <v>-12.86170561947018</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.66540942063705</v>
       </c>
       <c r="E97">
-        <v>-43.22978404736648</v>
+        <v>-44.52249808725508</v>
       </c>
       <c r="F97">
-        <v>-3.954247564309268</v>
+        <v>-2.053165912436876</v>
       </c>
       <c r="G97">
-        <v>-11.99561062712267</v>
+        <v>-13.25540231609139</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.99988541348525</v>
       </c>
       <c r="E98">
-        <v>-45.53443315324611</v>
+        <v>-46.87243193321142</v>
       </c>
       <c r="F98">
-        <v>-4.46647683150437</v>
+        <v>-2.221098350904211</v>
       </c>
       <c r="G98">
-        <v>-12.95059376719962</v>
+        <v>-12.67963885699243</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.3635860005209</v>
       </c>
       <c r="E99">
-        <v>-47.94386661918922</v>
+        <v>-47.81847317391683</v>
       </c>
       <c r="F99">
-        <v>-3.937518684609732</v>
+        <v>-2.370183774223052</v>
       </c>
       <c r="G99">
-        <v>-13.22944763906351</v>
+        <v>-13.05432640112714</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.76790074279511</v>
       </c>
       <c r="E100">
-        <v>-49.69766988253882</v>
+        <v>-49.92610648961875</v>
       </c>
       <c r="F100">
-        <v>-5.019807204124175</v>
+        <v>-2.571685801688838</v>
       </c>
       <c r="G100">
-        <v>-13.22612385134208</v>
+        <v>-13.46890270846453</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.16074877411758</v>
       </c>
       <c r="E101">
-        <v>-51.3218727482629</v>
+        <v>-51.74790365807502</v>
       </c>
       <c r="F101">
-        <v>-4.366827546417201</v>
+        <v>-2.87210566582512</v>
       </c>
       <c r="G101">
-        <v>-13.82532431758631</v>
+        <v>-13.41668878421915</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.60681661092988</v>
       </c>
       <c r="E102">
-        <v>-51.64939576298617</v>
+        <v>-53.66803211113385</v>
       </c>
       <c r="F102">
-        <v>-5.250191089455969</v>
+        <v>-2.848425955248693</v>
       </c>
       <c r="G102">
-        <v>-14.42690837661883</v>
+        <v>-13.21172297824625</v>
       </c>
     </row>
   </sheetData>
